--- a/reports/daily_report_20260315.xlsx
+++ b/reports/daily_report_20260315.xlsx
@@ -2812,14 +2812,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>最新日期: 2026-03-15 06:20:07.622569</t>
+          <t>最新日期: 2026-03-15 12:35:12.382336</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>数据天数: 7</t>
+          <t>数据天数: 8</t>
         </is>
       </c>
     </row>
@@ -4972,14 +4972,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>最新日期: 2026-03-15 06:20:07.624611</t>
+          <t>最新日期: 2026-03-15 12:35:12.384425</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>数据天数: 7</t>
+          <t>数据天数: 8</t>
         </is>
       </c>
     </row>
@@ -7128,14 +7128,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>最新日期: 2026-03-15 06:20:07.626302</t>
+          <t>最新日期: 2026-03-15 12:35:12.386174</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>数据天数: 7</t>
+          <t>数据天数: 8</t>
         </is>
       </c>
     </row>
@@ -9288,14 +9288,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>最新日期: 2026-03-15 06:20:07.627948</t>
+          <t>最新日期: 2026-03-15 12:35:12.387924</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>数据天数: 7</t>
+          <t>数据天数: 8</t>
         </is>
       </c>
     </row>
